--- a/consent_forms/039_permanent_makeup_consent_form--consent_forms.xlsx
+++ b/consent_forms/039_permanent_makeup_consent_form--consent_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -780,8 +780,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
-    <col width="37" customWidth="1" min="2" max="2"/>
-    <col width="37" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -809,12 +809,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_10,_'name':_'eyeliner'}</t>
+          <t>eyeliner</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 10, 'name': 'Eyeliner'}</t>
+          <t>Eyeliner</t>
         </is>
       </c>
     </row>
@@ -826,12 +826,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_11,_'name':_'eyebrow'}</t>
+          <t>eyebrow</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 11, 'name': 'Eyebrow'}</t>
+          <t>Eyebrow</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_12,_'name':_'liner'}</t>
+          <t>liner</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 12, 'name': 'Liner'}</t>
+          <t>Liner</t>
         </is>
       </c>
     </row>
@@ -860,12 +860,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_13,_'name':_'blush'}</t>
+          <t>blush</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 13, 'name': 'Blush'}</t>
+          <t>Blush</t>
         </is>
       </c>
     </row>
@@ -877,12 +877,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_14,_'name':_'lip'}</t>
+          <t>lip</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 14, 'name': 'Lip'}</t>
+          <t>Lip</t>
         </is>
       </c>
     </row>
@@ -894,12 +894,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_15,_'name':_'lip_liner'}</t>
+          <t>lip_liner</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 15, 'name': 'Lip Liner'}</t>
+          <t>Lip Liner</t>
         </is>
       </c>
     </row>
@@ -911,12 +911,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_16,_'name':_'microblading'}</t>
+          <t>microblading</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 16, 'name': 'Microblading'}</t>
+          <t>Microblading</t>
         </is>
       </c>
     </row>
@@ -928,12 +928,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_17,_'name':_'eyelid'}</t>
+          <t>eyelid</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 17, 'name': 'Eyelid'}</t>
+          <t>Eyelid</t>
         </is>
       </c>
     </row>
@@ -945,12 +945,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_22,_'name':_'cash'}</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 22, 'name': 'Cash'}</t>
+          <t>Cash</t>
         </is>
       </c>
     </row>
@@ -962,12 +962,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_23,_'name':_'bank_transfer'}</t>
+          <t>bank_transfer</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 23, 'name': 'Bank Transfer'}</t>
+          <t>Bank Transfer</t>
         </is>
       </c>
     </row>
@@ -979,12 +979,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_24,_'name':_'credit_card'}</t>
+          <t>credit_card</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 24, 'name': 'Credit Card'}</t>
+          <t>Credit Card</t>
         </is>
       </c>
     </row>
@@ -996,12 +996,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_26,_'name':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 26, 'name': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1013,12 +1013,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_27,_'name':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 27, 'name': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
